--- a/Result/profitability/6823.xlsx
+++ b/Result/profitability/6823.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM27"/>
+  <dimension ref="A1:AM28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3366,13 +3366,13 @@
         <v>136</v>
       </c>
       <c r="D24" t="n">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="E24" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F24" t="n">
-        <v>33.62</v>
+        <v>41.19</v>
       </c>
       <c r="G24" t="n">
         <v>25</v>
@@ -3398,7 +3398,7 @@
         <v>-1.2125</v>
       </c>
       <c r="N24" t="n">
-        <v>9.36875</v>
+        <v>10.315</v>
       </c>
       <c r="O24" t="n">
         <v>1</v>
@@ -3431,10 +3431,10 @@
         <v>-1.290697674418605</v>
       </c>
       <c r="Y24" t="n">
-        <v>18.9</v>
+        <v>26.47</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.283967391304348</v>
+        <v>1.798233695652174</v>
       </c>
       <c r="AA24" t="n">
         <v>2.26</v>
@@ -3443,10 +3443,10 @@
         <v>-1.284090909090909</v>
       </c>
       <c r="AC24" t="n">
-        <v>29.48</v>
+        <v>37.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>7.120772946859903</v>
+        <v>8.949275362318842</v>
       </c>
       <c r="AE24" t="n">
         <v>1</v>
@@ -3493,10 +3493,10 @@
         <v>198</v>
       </c>
       <c r="D25" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>-8</v>
       </c>
       <c r="F25" t="n">
         <v>0.9399999999999999</v>
@@ -3525,7 +3525,7 @@
         <v>-1.23625</v>
       </c>
       <c r="N25" t="n">
-        <v>8.303750000000001</v>
+        <v>9.25</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3558,10 +3558,10 @@
         <v>-5.5</v>
       </c>
       <c r="Y25" t="n">
-        <v>-32.68</v>
+        <v>-40.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>-0.9720404521118382</v>
+        <v>-0.9771789269240106</v>
       </c>
       <c r="AA25" t="n">
         <v>0.0299999999999998</v>
@@ -3652,7 +3652,7 @@
         <v>-1.9225</v>
       </c>
       <c r="N26" t="n">
-        <v>3.5375</v>
+        <v>4.483750000000001</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3779,7 +3779,7 @@
         <v>-2.055</v>
       </c>
       <c r="N27" t="n">
-        <v>1.62125</v>
+        <v>2.5675</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3857,6 +3857,133 @@
       </c>
       <c r="AM27" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6823</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>172</v>
+      </c>
+      <c r="D28" t="n">
+        <v>197</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-25</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-14.52</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-73</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>-42.23%</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>-67</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-69</v>
+      </c>
+      <c r="L28" t="n">
+        <v>-2.27</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-2.11875</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.2350000000000001</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0.1899999999999999</v>
+      </c>
+      <c r="X28" t="n">
+        <v>-0.07723577235772361</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>-0.8899999999999988</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0.0652971386647101</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-2.77</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>-5.54</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>-55.70999999999999</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>-1.35251274581209</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK28" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
